--- a/data/test_cases/role_test_cases.xlsx
+++ b/data/test_cases/role_test_cases.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="40">
   <si>
     <t>status</t>
   </si>
@@ -22,6 +22,9 @@
     <t>case_no</t>
   </si>
   <si>
+    <t>priority</t>
+  </si>
+  <si>
     <t>author</t>
   </si>
   <si>
@@ -52,12 +55,15 @@
     <t>note</t>
   </si>
   <si>
-    <t>Skip</t>
+    <t>Done</t>
   </si>
   <si>
     <t>Role01</t>
   </si>
   <si>
+    <t>Critical</t>
+  </si>
+  <si>
     <t>Nhat</t>
   </si>
   <si>
@@ -82,9 +88,6 @@
     <t>Note</t>
   </si>
   <si>
-    <t>Done</t>
-  </si>
-  <si>
     <t>Role02</t>
   </si>
   <si>
@@ -116,9 +119,6 @@
   </si>
   <si>
     <t>Role04</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>Edit current role</t>
@@ -170,12 +170,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -483,21 +480,22 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="3" width="6.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="3" width="12.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="3" width="7.433571428571429" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="3" width="6.433571428571429" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="3" width="13.576428571428572" customWidth="1" bestFit="1" hidden="1"/>
-    <col min="6" max="6" style="3" width="20.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="3" width="10.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="3" width="23.433571428571426" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="3" width="34.29071428571429" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="3" width="36.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="3" width="4.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="2" width="6.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="2" width="12.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="2" width="7.433571428571429" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="2" width="6.433571428571429" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="2" width="13.576428571428572" customWidth="1" bestFit="1" hidden="1"/>
+    <col min="7" max="7" style="2" width="20.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="2" width="10.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="2" width="23.433571428571426" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="2" width="34.29071428571429" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="2" width="36.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="2" width="4.862142857142857" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -537,88 +535,97 @@
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>21</v>
+      </c>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="K3" s="1"/>
+      <c r="I3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>29</v>
@@ -627,50 +634,54 @@
         <v>30</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K4" s="1"/>
+      <c r="K4" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="I5" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="J5" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="K5" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="K5" s="1"/>
       <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/test_cases/role_test_cases.xlsx
+++ b/data/test_cases/role_test_cases.xlsx
@@ -14,17 +14,20 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="42">
+  <si>
+    <t>case_no</t>
+  </si>
   <si>
     <t>status</t>
   </si>
   <si>
-    <t>case_no</t>
-  </si>
-  <si>
     <t>priority</t>
   </si>
   <si>
+    <t>case_type</t>
+  </si>
+  <si>
     <t>author</t>
   </si>
   <si>
@@ -55,15 +58,18 @@
     <t>note</t>
   </si>
   <si>
+    <t>Role01</t>
+  </si>
+  <si>
     <t>Done</t>
   </si>
   <si>
-    <t>Role01</t>
-  </si>
-  <si>
     <t>Critical</t>
   </si>
   <si>
+    <t>positive</t>
+  </si>
+  <si>
     <t>Nhat</t>
   </si>
   <si>
@@ -85,7 +91,7 @@
     <t>{"_id":"{admin_role_id}","status_code":200}</t>
   </si>
   <si>
-    <t>Note</t>
+    <t/>
   </si>
   <si>
     <t>Role02</t>
@@ -170,9 +176,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -480,22 +489,23 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="2" width="6.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="2" width="12.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="2" width="7.433571428571429" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="2" width="6.433571428571429" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="2" width="13.576428571428572" customWidth="1" bestFit="1" hidden="1"/>
-    <col min="7" max="7" style="2" width="20.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="2" width="10.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="2" width="23.433571428571426" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="2" width="34.29071428571429" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="2" width="36.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="2" width="4.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="3" width="6.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="3" width="12.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="3" width="7.433571428571429" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="3" width="6.433571428571429" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="3" width="13.576428571428572" customWidth="1" bestFit="1" hidden="1"/>
+    <col min="8" max="8" style="3" width="20.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="3" width="10.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="3" width="23.433571428571426" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="3" width="34.29071428571429" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="3" width="36.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="3" width="4.862142857142857" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -538,150 +548,165 @@
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>23</v>
+      </c>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M2" s="1"/>
+      <c r="N2" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="L3" s="1"/>
       <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="L4" s="1"/>
+        <v>34</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1" t="s">
-        <v>35</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="1"/>
       <c r="H5" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="L5" s="1"/>
+        <v>40</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>41</v>
+      </c>
       <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/test_cases/role_test_cases.xlsx
+++ b/data/test_cases/role_test_cases.xlsx
@@ -85,7 +85,7 @@
     <t>{"_id":"{admin_role_id}","status_code":200}</t>
   </si>
   <si>
-    <t>Note</t>
+    <t/>
   </si>
   <si>
     <t>Role02</t>
@@ -170,9 +170,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -483,19 +486,19 @@
   <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="2" width="6.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="2" width="12.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="2" width="7.433571428571429" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="2" width="6.433571428571429" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="2" width="13.576428571428572" customWidth="1" bestFit="1" hidden="1"/>
-    <col min="7" max="7" style="2" width="20.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="2" width="10.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="2" width="23.433571428571426" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="2" width="34.29071428571429" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="2" width="36.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="2" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="2" width="4.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="3" width="6.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="3" width="12.290714285714287" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="3" width="7.433571428571429" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="3" width="6.433571428571429" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="3" width="13.576428571428572" customWidth="1" bestFit="1" hidden="1"/>
+    <col min="7" max="7" style="3" width="20.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="3" width="10.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="3" width="23.433571428571426" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="3" width="34.29071428571429" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="3" width="36.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="3" width="4.862142857142857" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -572,7 +575,7 @@
         <v>22</v>
       </c>
       <c r="L2" s="1"/>
-      <c r="M2" s="1" t="s">
+      <c r="M2" s="2" t="s">
         <v>23</v>
       </c>
     </row>
